--- a/Human-JAVA/프로젝트PPT자료/1103_과제_명세서_김가율.xlsx
+++ b/Human-JAVA/프로젝트PPT자료/1103_과제_명세서_김가율.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuuri/Study/Human-JAVA/프로젝트PPT자료/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5494110-0B99-0E43-A243-2BD01C513A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4247C094-065C-C640-827E-5E1240F6F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19520" xr2:uid="{F6773DF6-F8C0-2C4E-B922-1CC374C99477}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="17280" windowHeight="19520" activeTab="1" xr2:uid="{F6773DF6-F8C0-2C4E-B922-1CC374C99477}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="157">
   <si>
     <t>Main</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -544,6 +545,118 @@
   </si>
   <si>
     <t>입력 직위가 목록에 있는지 여부 판단 후 결과 리턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김또또</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인사팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김대리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김부장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경영팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회계팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김인사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김회계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김경영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김주임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박사모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김대표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정회계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박과장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍주임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공과장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍부장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조임원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +664,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -592,6 +705,22 @@
     <font>
       <sz val="16"/>
       <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -702,7 +831,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -715,23 +844,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -754,9 +868,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -767,6 +878,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1083,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7C1820-04F5-A244-BC08-26CCDB17BCED}">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="23"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1"/>
@@ -1095,2086 +1245,1919 @@
     <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.625" style="1"/>
     <col min="9" max="9" width="56" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="4"/>
-    <col min="11" max="16384" width="10.625" style="5"/>
+    <col min="10" max="16384" width="10.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1">
-      <c r="A1" s="1"/>
+    <row r="1" spans="2:9">
       <c r="B1" s="2"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="8" spans="1:10" s="5" customFormat="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="6" t="s">
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="s">
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" s="1" customFormat="1">
-      <c r="B9" s="11" t="s">
+    </row>
+    <row r="9" spans="2:9" s="1" customFormat="1">
+      <c r="B9" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="5" customFormat="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12" t="s">
+    <row r="10" spans="2:9">
+      <c r="B10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="s">
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="14" spans="1:10" s="5" customFormat="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7" t="s">
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="17"/>
+      <c r="D14" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" s="5" customFormat="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="7" t="s">
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" s="5" customFormat="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="17" t="s">
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" s="5" customFormat="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="12" t="s">
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="s">
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" s="5" customFormat="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="18" t="s">
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="15" t="s">
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" s="5" customFormat="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="18" t="s">
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="15" t="s">
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" s="5" customFormat="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="18" t="s">
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="15" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" s="5" customFormat="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="20" t="s">
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="15" t="s">
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" s="5" customFormat="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="20" t="s">
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17" t="s">
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="15" t="s">
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" s="5" customFormat="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="17" t="s">
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" s="5" customFormat="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="17" t="s">
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" s="5" customFormat="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="17" t="s">
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" s="5" customFormat="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="17" t="s">
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="15" t="s">
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="30" spans="1:10" s="5" customFormat="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="7" t="s">
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="17"/>
+      <c r="D30" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" s="5" customFormat="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="7" t="s">
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="7" t="s">
+      <c r="C31" s="17"/>
+      <c r="D31" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" s="1" customFormat="1">
-      <c r="B32" s="17" t="s">
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="2:9" s="1" customFormat="1">
+      <c r="B32" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="5" customFormat="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="12" t="s">
+    <row r="33" spans="2:9">
+      <c r="B33" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="s">
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" s="5" customFormat="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="18" t="s">
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="9"/>
+      <c r="E34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="15" t="s">
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" s="5" customFormat="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="18" t="s">
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17" t="s">
+      <c r="D35" s="9"/>
+      <c r="E35" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="15" t="s">
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" s="5" customFormat="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="18" t="s">
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17" t="s">
+      <c r="D36" s="9"/>
+      <c r="E36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="15" t="s">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" s="5" customFormat="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="18" t="s">
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17" t="s">
+      <c r="D37" s="9"/>
+      <c r="E37" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="15" t="s">
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" s="5" customFormat="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="18" t="s">
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17" t="s">
+      <c r="D38" s="9"/>
+      <c r="E38" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="15" t="s">
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" s="5" customFormat="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="17" t="s">
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="9"/>
+      <c r="E39" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" s="5" customFormat="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="17" t="s">
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17" t="s">
+      <c r="D40" s="9"/>
+      <c r="E40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="15" t="s">
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" s="5" customFormat="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="17" t="s">
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17" t="s">
+      <c r="D41" s="9"/>
+      <c r="E41" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="G41" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" s="5" customFormat="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="17" t="s">
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17" t="s">
+      <c r="D42" s="9"/>
+      <c r="E42" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="15" t="s">
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" s="5" customFormat="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="17" t="s">
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17" t="s">
+      <c r="D43" s="9"/>
+      <c r="E43" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H43" s="17" t="s">
+      <c r="H43" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" s="5" customFormat="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="17" t="s">
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17" t="s">
+      <c r="D44" s="9"/>
+      <c r="E44" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="15" t="s">
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" s="5" customFormat="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="17" t="s">
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17" t="s">
+      <c r="D45" s="9"/>
+      <c r="E45" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="17" t="s">
+      <c r="H45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="I45" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" s="5" customFormat="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="17" t="s">
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17" t="s">
+      <c r="D46" s="9"/>
+      <c r="E46" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="15" t="s">
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" s="5" customFormat="1">
-      <c r="A47" s="1"/>
-      <c r="B47" s="17" t="s">
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17" t="s">
+      <c r="D47" s="9"/>
+      <c r="E47" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="G47" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="17" t="s">
+      <c r="H47" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" s="5" customFormat="1">
-      <c r="A48" s="1"/>
-      <c r="B48" s="17" t="s">
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="9"/>
+      <c r="E48" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="15" t="s">
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="51" spans="1:10" s="5" customFormat="1">
-      <c r="A51" s="1"/>
-      <c r="B51" s="7" t="s">
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="7" t="s">
+      <c r="C51" s="17"/>
+      <c r="D51" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" s="5" customFormat="1">
-      <c r="A52" s="1"/>
-      <c r="B52" s="7" t="s">
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="11"/>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="7" t="s">
+      <c r="C52" s="17"/>
+      <c r="D52" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" s="1" customFormat="1">
-      <c r="B53" s="17" t="s">
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53" spans="2:9" s="1" customFormat="1">
+      <c r="B53" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="5" customFormat="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="12" t="s">
+    <row r="54" spans="2:9">
+      <c r="B54" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="s">
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" s="5" customFormat="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="18" t="s">
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="9"/>
+      <c r="E55" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="15" t="s">
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" s="5" customFormat="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="21" t="s">
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17" t="s">
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="15" t="s">
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" s="5" customFormat="1">
-      <c r="A57" s="1"/>
-      <c r="B57" s="20" t="s">
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="9"/>
+      <c r="E57" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="15" t="s">
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="60" spans="1:10" s="5" customFormat="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="7" t="s">
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="7" t="s">
+      <c r="C60" s="17"/>
+      <c r="D60" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" s="5" customFormat="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="7" t="s">
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="7" t="s">
+      <c r="C61" s="17"/>
+      <c r="D61" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="16"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" s="1" customFormat="1">
-      <c r="B62" s="17" t="s">
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="11"/>
+    </row>
+    <row r="62" spans="2:9" s="1" customFormat="1">
+      <c r="B62" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F62" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="17" t="s">
+      <c r="H62" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I62" s="17" t="s">
+      <c r="I62" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="5" customFormat="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="12" t="s">
+    <row r="63" spans="2:9">
+      <c r="B63" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="s">
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" s="5" customFormat="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="18" t="s">
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17" t="s">
+      <c r="D64" s="9"/>
+      <c r="E64" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="15" t="s">
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J64" s="4"/>
-    </row>
-    <row r="65" spans="1:10" s="5" customFormat="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="18" t="s">
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17" t="s">
+      <c r="D65" s="9"/>
+      <c r="E65" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="15" t="s">
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="1:10" s="5" customFormat="1">
-      <c r="A66" s="1"/>
-      <c r="B66" s="21" t="s">
+    </row>
+    <row r="66" spans="2:9">
+      <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17" t="s">
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="15" t="s">
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="J66" s="4"/>
-    </row>
-    <row r="67" spans="1:10" s="5" customFormat="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="20" t="s">
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17" t="s">
+      <c r="D67" s="9"/>
+      <c r="E67" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="15" t="s">
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="J67" s="4"/>
-    </row>
-    <row r="70" spans="1:10" s="5" customFormat="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="7" t="s">
+    </row>
+    <row r="70" spans="2:9">
+      <c r="B70" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="7" t="s">
+      <c r="C70" s="17"/>
+      <c r="D70" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="16"/>
-      <c r="J70" s="4"/>
-    </row>
-    <row r="71" spans="1:10" s="5" customFormat="1">
-      <c r="A71" s="1"/>
-      <c r="B71" s="7" t="s">
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="11"/>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="B71" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="7" t="s">
+      <c r="C71" s="17"/>
+      <c r="D71" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="4"/>
-    </row>
-    <row r="72" spans="1:10" s="1" customFormat="1">
-      <c r="B72" s="17" t="s">
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="11"/>
+    </row>
+    <row r="72" spans="2:9" s="1" customFormat="1">
+      <c r="B72" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G72" s="17" t="s">
+      <c r="G72" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H72" s="17" t="s">
+      <c r="H72" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I72" s="17" t="s">
+      <c r="I72" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="5" customFormat="1">
-      <c r="A73" s="1"/>
-      <c r="B73" s="12" t="s">
+    <row r="73" spans="2:9">
+      <c r="B73" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="s">
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="J73" s="4"/>
-    </row>
-    <row r="74" spans="1:10" s="5" customFormat="1">
-      <c r="A74" s="1"/>
-      <c r="B74" s="18" t="s">
+    </row>
+    <row r="74" spans="2:9">
+      <c r="B74" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C74" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D74" s="17"/>
-      <c r="E74" s="17" t="s">
+      <c r="D74" s="9"/>
+      <c r="E74" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F74" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="15" t="s">
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J74" s="4"/>
-    </row>
-    <row r="75" spans="1:10" s="5" customFormat="1">
-      <c r="A75" s="1"/>
-      <c r="B75" s="18" t="s">
+    </row>
+    <row r="75" spans="2:9">
+      <c r="B75" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D75" s="17"/>
-      <c r="E75" s="17" t="s">
+      <c r="D75" s="9"/>
+      <c r="E75" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G75" s="17"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="15" t="s">
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" s="5" customFormat="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="18" t="s">
+    </row>
+    <row r="76" spans="2:9">
+      <c r="B76" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C76" s="19" t="s">
+      <c r="C76" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17" t="s">
+      <c r="D76" s="9"/>
+      <c r="E76" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F76" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G76" s="17"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="15" t="s">
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J76" s="4"/>
-    </row>
-    <row r="77" spans="1:10" s="5" customFormat="1">
-      <c r="A77" s="1"/>
-      <c r="B77" s="18" t="s">
+    </row>
+    <row r="77" spans="2:9">
+      <c r="B77" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17" t="s">
+      <c r="D77" s="9"/>
+      <c r="E77" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F77" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="15" t="s">
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" s="5" customFormat="1">
-      <c r="A78" s="1"/>
-      <c r="B78" s="21" t="s">
+    </row>
+    <row r="78" spans="2:9">
+      <c r="B78" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17" t="s">
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="15" t="s">
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="J78" s="4"/>
-    </row>
-    <row r="79" spans="1:10" s="5" customFormat="1">
-      <c r="A79" s="1"/>
-      <c r="B79" s="20" t="s">
+    </row>
+    <row r="79" spans="2:9">
+      <c r="B79" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="19" t="s">
+      <c r="C79" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17" t="s">
+      <c r="D79" s="9"/>
+      <c r="E79" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F79" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="15" t="s">
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J79" s="4"/>
-    </row>
-    <row r="80" spans="1:10" s="5" customFormat="1">
-      <c r="A80" s="1"/>
-      <c r="B80" s="20" t="s">
+    </row>
+    <row r="80" spans="2:9">
+      <c r="B80" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17" t="s">
+      <c r="D80" s="9"/>
+      <c r="E80" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F80" s="17" t="s">
+      <c r="F80" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G80" s="17" t="s">
+      <c r="G80" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H80" s="17" t="s">
+      <c r="H80" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I80" s="15" t="s">
+      <c r="I80" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="J80" s="4"/>
-    </row>
-    <row r="83" spans="1:10" s="5" customFormat="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="7" t="s">
+    </row>
+    <row r="83" spans="2:9">
+      <c r="B83" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="7" t="s">
+      <c r="C83" s="17"/>
+      <c r="D83" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" s="5" customFormat="1">
-      <c r="A84" s="1"/>
-      <c r="B84" s="7" t="s">
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="11"/>
+    </row>
+    <row r="84" spans="2:9">
+      <c r="B84" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="9"/>
-      <c r="D84" s="7" t="s">
+      <c r="C84" s="17"/>
+      <c r="D84" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="16"/>
-      <c r="J84" s="4"/>
-    </row>
-    <row r="85" spans="1:10" s="1" customFormat="1">
-      <c r="B85" s="17" t="s">
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="11"/>
+    </row>
+    <row r="85" spans="2:9" s="1" customFormat="1">
+      <c r="B85" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="G85" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H85" s="17" t="s">
+      <c r="H85" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I85" s="17" t="s">
+      <c r="I85" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:10" s="5" customFormat="1">
-      <c r="A86" s="1"/>
-      <c r="B86" s="12" t="s">
+    <row r="86" spans="2:9">
+      <c r="B86" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D86" s="14" t="s">
+      <c r="D86" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="15" t="s">
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="19"/>
+      <c r="H86" s="19"/>
+      <c r="I86" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J86" s="4"/>
-    </row>
-    <row r="87" spans="1:10" s="5" customFormat="1">
-      <c r="A87" s="1"/>
-      <c r="B87" s="18" t="s">
+    </row>
+    <row r="87" spans="2:9">
+      <c r="B87" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C87" s="19" t="s">
+      <c r="C87" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17" t="s">
+      <c r="D87" s="9"/>
+      <c r="E87" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F87" s="17" t="s">
+      <c r="F87" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G87" s="17"/>
-      <c r="H87" s="17"/>
-      <c r="I87" s="15" t="s">
+      <c r="G87" s="9"/>
+      <c r="H87" s="9"/>
+      <c r="I87" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J87" s="4"/>
-    </row>
-    <row r="88" spans="1:10" s="5" customFormat="1">
-      <c r="A88" s="1"/>
-      <c r="B88" s="18" t="s">
+    </row>
+    <row r="88" spans="2:9">
+      <c r="B88" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17" t="s">
+      <c r="D88" s="9"/>
+      <c r="E88" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F88" s="17" t="s">
+      <c r="F88" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G88" s="17"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="15" t="s">
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J88" s="4"/>
-    </row>
-    <row r="89" spans="1:10" s="5" customFormat="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="21" t="s">
+    </row>
+    <row r="89" spans="2:9">
+      <c r="B89" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C89" s="17" t="s">
+      <c r="C89" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17" t="s">
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="G89" s="17"/>
-      <c r="H89" s="17"/>
-      <c r="I89" s="15" t="s">
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="J89" s="4"/>
-    </row>
-    <row r="90" spans="1:10" s="5" customFormat="1">
-      <c r="A90" s="1"/>
-      <c r="B90" s="20" t="s">
+    </row>
+    <row r="90" spans="2:9">
+      <c r="B90" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="19" t="s">
+      <c r="C90" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D90" s="17"/>
-      <c r="E90" s="17" t="s">
+      <c r="D90" s="9"/>
+      <c r="E90" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F90" s="17" t="s">
+      <c r="F90" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="G90" s="17"/>
-      <c r="H90" s="17"/>
-      <c r="I90" s="15" t="s">
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J90" s="4"/>
-    </row>
-    <row r="93" spans="1:10" s="5" customFormat="1">
-      <c r="A93" s="1"/>
-      <c r="B93" s="7" t="s">
+    </row>
+    <row r="93" spans="2:9">
+      <c r="B93" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="7" t="s">
+      <c r="C93" s="17"/>
+      <c r="D93" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="16"/>
-      <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:10" s="5" customFormat="1">
-      <c r="A94" s="1"/>
-      <c r="B94" s="7" t="s">
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="17"/>
+      <c r="I93" s="11"/>
+    </row>
+    <row r="94" spans="2:9">
+      <c r="B94" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C94" s="9"/>
-      <c r="D94" s="7" t="s">
+      <c r="C94" s="17"/>
+      <c r="D94" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="16"/>
-      <c r="J94" s="4"/>
-    </row>
-    <row r="95" spans="1:10" s="1" customFormat="1">
-      <c r="B95" s="17" t="s">
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="17"/>
+      <c r="I94" s="11"/>
+    </row>
+    <row r="95" spans="2:9" s="1" customFormat="1">
+      <c r="B95" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F95" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G95" s="17" t="s">
+      <c r="G95" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H95" s="17" t="s">
+      <c r="H95" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I95" s="17" t="s">
+      <c r="I95" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="96" spans="1:10" s="5" customFormat="1">
-      <c r="A96" s="1"/>
-      <c r="B96" s="12" t="s">
+    <row r="96" spans="2:9">
+      <c r="B96" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
-      <c r="H96" s="14"/>
-      <c r="I96" s="15" t="s">
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J96" s="4"/>
-    </row>
-    <row r="97" spans="1:10" s="5" customFormat="1">
-      <c r="A97" s="1"/>
-      <c r="B97" s="18" t="s">
+    </row>
+    <row r="97" spans="2:9">
+      <c r="B97" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C97" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17" t="s">
+      <c r="D97" s="9"/>
+      <c r="E97" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F97" s="17" t="s">
+      <c r="F97" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="15" t="s">
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
+      <c r="I97" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="4"/>
-    </row>
-    <row r="98" spans="1:10" s="5" customFormat="1">
-      <c r="A98" s="1"/>
-      <c r="B98" s="18" t="s">
+    </row>
+    <row r="98" spans="2:9">
+      <c r="B98" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="19" t="s">
+      <c r="C98" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D98" s="17"/>
-      <c r="E98" s="17" t="s">
+      <c r="D98" s="9"/>
+      <c r="E98" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G98" s="17"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="15" t="s">
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
+      <c r="I98" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J98" s="4"/>
-    </row>
-    <row r="99" spans="1:10" s="5" customFormat="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="18" t="s">
+    </row>
+    <row r="99" spans="2:9">
+      <c r="B99" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17" t="s">
+      <c r="D99" s="9"/>
+      <c r="E99" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F99" s="17" t="s">
+      <c r="F99" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G99" s="17"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="15" t="s">
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" s="5" customFormat="1">
-      <c r="A100" s="1"/>
-      <c r="B100" s="21" t="s">
+    </row>
+    <row r="100" spans="2:9">
+      <c r="B100" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C100" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="17" t="s">
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="G100" s="17"/>
-      <c r="H100" s="17"/>
-      <c r="I100" s="15" t="s">
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
+      <c r="I100" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J100" s="4"/>
-    </row>
-    <row r="101" spans="1:10" s="5" customFormat="1">
-      <c r="A101" s="1"/>
-      <c r="B101" s="20" t="s">
+    </row>
+    <row r="101" spans="2:9">
+      <c r="B101" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D101" s="17"/>
-      <c r="E101" s="17" t="s">
+      <c r="D101" s="9"/>
+      <c r="E101" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G101" s="17"/>
-      <c r="H101" s="17"/>
-      <c r="I101" s="15" t="s">
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
+      <c r="I101" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J101" s="4"/>
-    </row>
-    <row r="102" spans="1:10" s="5" customFormat="1">
-      <c r="A102" s="1"/>
-      <c r="B102" s="20" t="s">
+    </row>
+    <row r="102" spans="2:9">
+      <c r="B102" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C102" s="19" t="s">
+      <c r="C102" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D102" s="17"/>
-      <c r="E102" s="17" t="s">
+      <c r="D102" s="9"/>
+      <c r="E102" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F102" s="17" t="s">
+      <c r="F102" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G102" s="17" t="s">
+      <c r="G102" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H102" s="17" t="s">
+      <c r="H102" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I102" s="15" t="s">
+      <c r="I102" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="J102" s="4"/>
-    </row>
-    <row r="103" spans="1:10" s="5" customFormat="1">
-      <c r="A103" s="1"/>
-      <c r="B103" s="20" t="s">
+    </row>
+    <row r="103" spans="2:9">
+      <c r="B103" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D103" s="17"/>
-      <c r="E103" s="17" t="s">
+      <c r="D103" s="9"/>
+      <c r="E103" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F103" s="17" t="s">
+      <c r="F103" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="G103" s="17"/>
-      <c r="H103" s="17"/>
-      <c r="I103" s="15" t="s">
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
+      <c r="I103" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="J103" s="4"/>
-    </row>
-    <row r="106" spans="1:10" s="5" customFormat="1">
-      <c r="A106" s="1"/>
-      <c r="B106" s="7" t="s">
+    </row>
+    <row r="106" spans="2:9">
+      <c r="B106" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C106" s="9"/>
-      <c r="D106" s="7" t="s">
+      <c r="C106" s="17"/>
+      <c r="D106" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="16"/>
-      <c r="J106" s="4"/>
-    </row>
-    <row r="107" spans="1:10" s="5" customFormat="1">
-      <c r="A107" s="1"/>
-      <c r="B107" s="7" t="s">
+      <c r="E106" s="18"/>
+      <c r="F106" s="18"/>
+      <c r="G106" s="18"/>
+      <c r="H106" s="17"/>
+      <c r="I106" s="11"/>
+    </row>
+    <row r="107" spans="2:9">
+      <c r="B107" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C107" s="9"/>
-      <c r="D107" s="7" t="s">
+      <c r="C107" s="17"/>
+      <c r="D107" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="16"/>
-      <c r="J107" s="4"/>
-    </row>
-    <row r="108" spans="1:10" s="1" customFormat="1">
-      <c r="B108" s="17" t="s">
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
+      <c r="H107" s="17"/>
+      <c r="I107" s="11"/>
+    </row>
+    <row r="108" spans="2:9" s="1" customFormat="1">
+      <c r="B108" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C108" s="17" t="s">
+      <c r="C108" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E108" s="17" t="s">
+      <c r="E108" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F108" s="17" t="s">
+      <c r="F108" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G108" s="17" t="s">
+      <c r="G108" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H108" s="17" t="s">
+      <c r="H108" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I108" s="17" t="s">
+      <c r="I108" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="109" spans="1:10" s="5" customFormat="1">
-      <c r="A109" s="1"/>
-      <c r="B109" s="12" t="s">
+    <row r="109" spans="2:9">
+      <c r="B109" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D109" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
-      <c r="H109" s="14"/>
-      <c r="I109" s="15" t="s">
+      <c r="E109" s="19"/>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19"/>
+      <c r="H109" s="19"/>
+      <c r="I109" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="J109" s="4"/>
-    </row>
-    <row r="110" spans="1:10" s="5" customFormat="1">
-      <c r="A110" s="1"/>
-      <c r="B110" s="18" t="s">
+    </row>
+    <row r="110" spans="2:9">
+      <c r="B110" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C110" s="19" t="s">
+      <c r="C110" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D110" s="17"/>
-      <c r="E110" s="17" t="s">
+      <c r="D110" s="9"/>
+      <c r="E110" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G110" s="17"/>
-      <c r="H110" s="17"/>
-      <c r="I110" s="15" t="s">
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J110" s="4"/>
-    </row>
-    <row r="111" spans="1:10" s="5" customFormat="1">
-      <c r="A111" s="1"/>
-      <c r="B111" s="18" t="s">
+    </row>
+    <row r="111" spans="2:9">
+      <c r="B111" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D111" s="17"/>
-      <c r="E111" s="17" t="s">
+      <c r="D111" s="9"/>
+      <c r="E111" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G111" s="17"/>
-      <c r="H111" s="17"/>
-      <c r="I111" s="15" t="s">
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
+      <c r="I111" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J111" s="4"/>
-    </row>
-    <row r="112" spans="1:10" s="5" customFormat="1">
-      <c r="A112" s="1"/>
-      <c r="B112" s="18" t="s">
+    </row>
+    <row r="112" spans="2:9">
+      <c r="B112" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C112" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D112" s="17"/>
-      <c r="E112" s="17" t="s">
+      <c r="D112" s="9"/>
+      <c r="E112" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="G112" s="17"/>
-      <c r="H112" s="17"/>
-      <c r="I112" s="15" t="s">
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="J112" s="4"/>
-    </row>
-    <row r="113" spans="1:10" s="5" customFormat="1">
-      <c r="A113" s="1"/>
-      <c r="B113" s="18" t="s">
+    </row>
+    <row r="113" spans="2:9">
+      <c r="B113" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D113" s="17"/>
-      <c r="E113" s="17" t="s">
+      <c r="D113" s="9"/>
+      <c r="E113" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F113" s="17" t="s">
+      <c r="F113" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="17"/>
-      <c r="H113" s="17"/>
-      <c r="I113" s="15" t="s">
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
+      <c r="I113" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="J113" s="4"/>
-    </row>
-    <row r="114" spans="1:10" s="5" customFormat="1">
-      <c r="A114" s="1"/>
-      <c r="B114" s="20" t="s">
+    </row>
+    <row r="114" spans="2:9">
+      <c r="B114" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D114" s="17"/>
-      <c r="E114" s="17" t="s">
+      <c r="D114" s="9"/>
+      <c r="E114" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F114" s="17" t="s">
+      <c r="F114" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G114" s="17" t="s">
+      <c r="G114" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H114" s="17"/>
-      <c r="I114" s="15" t="s">
+      <c r="H114" s="9"/>
+      <c r="I114" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="J114" s="4"/>
-    </row>
-    <row r="115" spans="1:10" s="5" customFormat="1">
-      <c r="A115" s="1"/>
-      <c r="B115" s="20" t="s">
+    </row>
+    <row r="115" spans="2:9">
+      <c r="B115" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D115" s="17"/>
-      <c r="E115" s="17" t="s">
+      <c r="D115" s="9"/>
+      <c r="E115" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F115" s="17" t="s">
+      <c r="F115" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G115" s="17" t="s">
+      <c r="G115" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H115" s="17" t="s">
+      <c r="H115" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I115" s="15" t="s">
+      <c r="I115" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="J115" s="4"/>
-    </row>
-    <row r="116" spans="1:10" s="5" customFormat="1">
-      <c r="A116" s="1"/>
-      <c r="B116" s="20" t="s">
+    </row>
+    <row r="116" spans="2:9">
+      <c r="B116" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D116" s="17"/>
-      <c r="E116" s="17" t="s">
+      <c r="D116" s="9"/>
+      <c r="E116" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F116" s="17" t="s">
+      <c r="F116" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G116" s="17" t="s">
+      <c r="G116" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H116" s="17" t="s">
+      <c r="H116" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I116" s="15" t="s">
+      <c r="I116" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="J116" s="4"/>
-    </row>
-    <row r="117" spans="1:10" s="5" customFormat="1">
-      <c r="A117" s="1"/>
-      <c r="B117" s="20" t="s">
+    </row>
+    <row r="117" spans="2:9">
+      <c r="B117" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D117" s="17"/>
-      <c r="E117" s="17" t="s">
+      <c r="D117" s="9"/>
+      <c r="E117" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F117" s="17" t="s">
+      <c r="F117" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="G117" s="17" t="s">
+      <c r="G117" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H117" s="17" t="s">
+      <c r="H117" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I117" s="15" t="s">
+      <c r="I117" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J117" s="4"/>
-    </row>
-    <row r="118" spans="1:10" s="5" customFormat="1">
-      <c r="A118" s="1"/>
-      <c r="B118" s="20" t="s">
+    </row>
+    <row r="118" spans="2:9">
+      <c r="B118" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C118" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D118" s="17"/>
-      <c r="E118" s="17" t="s">
+      <c r="D118" s="9"/>
+      <c r="E118" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="17" t="s">
+      <c r="F118" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G118" s="17" t="s">
+      <c r="G118" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H118" s="17"/>
-      <c r="I118" s="15" t="s">
+      <c r="H118" s="9"/>
+      <c r="I118" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="J118" s="4"/>
-    </row>
-    <row r="119" spans="1:10" s="5" customFormat="1">
-      <c r="A119" s="1"/>
-      <c r="B119" s="20" t="s">
+    </row>
+    <row r="119" spans="2:9">
+      <c r="B119" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17" t="s">
+      <c r="D119" s="9"/>
+      <c r="E119" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F119" s="17" t="s">
+      <c r="F119" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G119" s="17" t="s">
+      <c r="G119" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H119" s="17" t="s">
+      <c r="H119" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I119" s="15" t="s">
+      <c r="I119" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="J119" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:H106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="D107:H107"/>
-    <mergeCell ref="D109:H109"/>
-    <mergeCell ref="D86:H86"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:H93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="D94:H94"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D63:H63"/>
     <mergeCell ref="D96:H96"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="D71:H71"/>
@@ -3183,33 +3166,629 @@
     <mergeCell ref="D83:H83"/>
     <mergeCell ref="B84:C84"/>
     <mergeCell ref="D84:H84"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D86:H86"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:H93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:H94"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:H106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:H107"/>
+    <mergeCell ref="D109:H109"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FD2DF1C-A114-0140-B1CB-F7E33B2E0646}">
+  <dimension ref="B4:N44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="4" width="10.625" style="22"/>
+    <col min="5" max="5" width="10.625" style="24"/>
+    <col min="6" max="6" width="2.5" style="22" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="22"/>
+    <col min="8" max="8" width="10.625" style="24"/>
+    <col min="9" max="9" width="2.5" style="22" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="22"/>
+    <col min="11" max="11" width="10.625" style="24"/>
+    <col min="12" max="12" width="2.5" style="22" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="22"/>
+    <col min="14" max="14" width="10.625" style="24"/>
+    <col min="15" max="15" width="2.5" style="22" customWidth="1"/>
+    <col min="16" max="16384" width="10.625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:14">
+      <c r="B4" s="21"/>
+      <c r="D4" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="23">
+        <v>1234</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="23">
+        <v>1</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="23">
+        <v>111</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="21"/>
+      <c r="D5" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="21"/>
+      <c r="D6" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="23">
+        <v>40</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H6" s="23">
+        <v>59</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="23">
+        <v>42</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="N6" s="23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="21"/>
+      <c r="D7" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="21"/>
+      <c r="D8" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="21"/>
+      <c r="D10" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="23">
+        <v>2331</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="23">
+        <v>2</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="23">
+        <v>1228</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="21"/>
+      <c r="D11" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12" s="21"/>
+      <c r="D12" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="23">
+        <v>31</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="23">
+        <v>55</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="23">
+        <v>38</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="N12" s="23">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="21"/>
+      <c r="D13" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" s="21"/>
+      <c r="D14" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" s="21"/>
+      <c r="D16" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="23">
+        <v>1222</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="23">
+        <v>2334</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" s="23">
+        <v>2111</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="23">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="21"/>
+      <c r="D17" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="21"/>
+      <c r="D18" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="23">
+        <v>35</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="23">
+        <v>34</v>
+      </c>
+      <c r="J18" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18" s="23">
+        <v>31</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="N18" s="23">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="21"/>
+      <c r="D19" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="21"/>
+      <c r="D20" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="21"/>
+      <c r="D22" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="23">
+        <v>1212</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="23">
+        <v>2999</v>
+      </c>
+      <c r="J22" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="23">
+        <v>2555</v>
+      </c>
+      <c r="M22" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="23">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="21"/>
+      <c r="D23" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="J23" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="M23" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="N23" s="23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="21"/>
+      <c r="D24" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="23">
+        <v>45</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="J24" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="23">
+        <v>26</v>
+      </c>
+      <c r="M24" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="N24" s="23">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="21"/>
+      <c r="D25" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="M25" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="N25" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="21"/>
+      <c r="D26" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M26" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="21"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="21"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="21"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="21"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="21"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="21"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="21"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="21"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="21"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="21"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="21"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="21"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="21"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="21"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="21"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>